--- a/artfynd/A 47128-2025 artfynd.xlsx
+++ b/artfynd/A 47128-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129809219</v>
+        <v>129809835</v>
       </c>
       <c r="B2" t="n">
         <v>79081</v>
@@ -704,16 +704,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496160</v>
+        <v>496132</v>
       </c>
       <c r="R2" t="n">
-        <v>7040028</v>
+        <v>7040056</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,71 +757,89 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129809838</v>
+        <v>129809219</v>
       </c>
       <c r="B3" t="n">
-        <v>100963</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496154</v>
+        <v>496160</v>
       </c>
       <c r="R3" t="n">
-        <v>7040081</v>
+        <v>7040028</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,66 +880,60 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129809835</v>
+        <v>129809838</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>100963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -926,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496132</v>
+        <v>496154</v>
       </c>
       <c r="R4" t="n">
-        <v>7040056</v>
+        <v>7040081</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,24 +994,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1851,32 +1851,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129809218</v>
+        <v>129809216</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>80146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496187</v>
+        <v>496144</v>
       </c>
       <c r="R13" t="n">
-        <v>7040066</v>
+        <v>7040037</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,32 +1948,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129809216</v>
+        <v>129809218</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496144</v>
+        <v>496187</v>
       </c>
       <c r="R14" t="n">
-        <v>7040037</v>
+        <v>7040066</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 47128-2025 artfynd.xlsx
+++ b/artfynd/A 47128-2025 artfynd.xlsx
@@ -1014,45 +1014,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129809205</v>
+        <v>129809837</v>
       </c>
       <c r="B5" t="n">
-        <v>91593</v>
+        <v>100963</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496150</v>
+        <v>496143</v>
       </c>
       <c r="R5" t="n">
-        <v>7040206</v>
+        <v>7040098</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,71 +1101,69 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129809837</v>
+        <v>129809205</v>
       </c>
       <c r="B6" t="n">
-        <v>100963</v>
+        <v>91593</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496143</v>
+        <v>496150</v>
       </c>
       <c r="R6" t="n">
-        <v>7040098</v>
+        <v>7040206</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,24 +1204,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129809209</v>
+        <v>129809214</v>
       </c>
       <c r="B8" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,34 +1359,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496144</v>
+        <v>496148</v>
       </c>
       <c r="R8" t="n">
-        <v>7040040</v>
+        <v>7040178</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,7 +1431,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Med apotechier</t>
+          <t>Färska ringhack högt upp på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129809214</v>
+        <v>129809209</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,42 +1469,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496148</v>
+        <v>496144</v>
       </c>
       <c r="R9" t="n">
-        <v>7040178</v>
+        <v>7040040</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack högt upp på gran</t>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1851,32 +1851,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129809216</v>
+        <v>129809218</v>
       </c>
       <c r="B13" t="n">
-        <v>80146</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496144</v>
+        <v>496187</v>
       </c>
       <c r="R13" t="n">
-        <v>7040037</v>
+        <v>7040066</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,32 +1948,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129809218</v>
+        <v>129809216</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496187</v>
+        <v>496144</v>
       </c>
       <c r="R14" t="n">
-        <v>7040066</v>
+        <v>7040037</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129809204</v>
+        <v>129809831</v>
       </c>
       <c r="B18" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2415,34 +2415,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496151</v>
+        <v>496065</v>
       </c>
       <c r="R18" t="n">
-        <v>7040043</v>
+        <v>7040037</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,28 +2486,54 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129809831</v>
+        <v>129809204</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>83050</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2512,37 +2541,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496065</v>
+        <v>496151</v>
       </c>
       <c r="R19" t="n">
-        <v>7040037</v>
+        <v>7040043</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,44 +2609,18 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2855,34 +2855,30 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129809206</v>
+        <v>129809217</v>
       </c>
       <c r="B22" t="n">
-        <v>80215</v>
+        <v>91613</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2890,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496146</v>
+        <v>496090</v>
       </c>
       <c r="R22" t="n">
-        <v>7040041</v>
+        <v>7040205</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2952,30 +2948,34 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129809217</v>
+        <v>129809206</v>
       </c>
       <c r="B23" t="n">
-        <v>91613</v>
+        <v>80215</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496090</v>
+        <v>496146</v>
       </c>
       <c r="R23" t="n">
-        <v>7040205</v>
+        <v>7040041</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 47128-2025 artfynd.xlsx
+++ b/artfynd/A 47128-2025 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>129809838</v>
       </c>
       <c r="B4" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129809837</v>
       </c>
       <c r="B5" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>129809205</v>
       </c>
       <c r="B6" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129809214</v>
+        <v>129809209</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,42 +1359,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496148</v>
+        <v>496144</v>
       </c>
       <c r="R8" t="n">
-        <v>7040178</v>
+        <v>7040040</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1423,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack högt upp på gran</t>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129809209</v>
+        <v>129809214</v>
       </c>
       <c r="B9" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,34 +1461,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496144</v>
+        <v>496148</v>
       </c>
       <c r="R9" t="n">
-        <v>7040040</v>
+        <v>7040178</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Med apotechier</t>
+          <t>Färska ringhack högt upp på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2314,7 +2314,7 @@
         <v>129809211</v>
       </c>
       <c r="B17" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129809831</v>
+        <v>129809204</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>83050</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2415,37 +2415,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496065</v>
+        <v>496151</v>
       </c>
       <c r="R18" t="n">
-        <v>7040037</v>
+        <v>7040043</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,54 +2483,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129809204</v>
+        <v>129809831</v>
       </c>
       <c r="B19" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2541,34 +2512,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496151</v>
+        <v>496065</v>
       </c>
       <c r="R19" t="n">
-        <v>7040043</v>
+        <v>7040037</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2609,18 +2583,44 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2630,7 +2630,7 @@
         <v>129809213</v>
       </c>
       <c r="B20" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2855,30 +2855,34 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129809217</v>
+        <v>129809206</v>
       </c>
       <c r="B22" t="n">
-        <v>91613</v>
+        <v>80215</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2886,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496090</v>
+        <v>496146</v>
       </c>
       <c r="R22" t="n">
-        <v>7040205</v>
+        <v>7040041</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2948,34 +2952,30 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129809206</v>
+        <v>129809217</v>
       </c>
       <c r="B23" t="n">
-        <v>80215</v>
+        <v>91617</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496146</v>
+        <v>496090</v>
       </c>
       <c r="R23" t="n">
-        <v>7040041</v>
+        <v>7040205</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3048,7 +3048,7 @@
         <v>129809212</v>
       </c>
       <c r="B24" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 47128-2025 artfynd.xlsx
+++ b/artfynd/A 47128-2025 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>129809838</v>
       </c>
       <c r="B4" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,42 +1014,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129809837</v>
+        <v>129809833</v>
       </c>
       <c r="B5" t="n">
-        <v>100967</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1057,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496143</v>
+        <v>496073</v>
       </c>
       <c r="R5" t="n">
-        <v>7040098</v>
+        <v>7040125</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,7 +1102,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1128,7 +1143,7 @@
         <v>129809205</v>
       </c>
       <c r="B6" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,37 +1237,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129809833</v>
+        <v>129809837</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>100969</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1260,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496073</v>
+        <v>496143</v>
       </c>
       <c r="R7" t="n">
-        <v>7040125</v>
+        <v>7040098</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,27 +1330,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -2314,7 +2314,7 @@
         <v>129809211</v>
       </c>
       <c r="B17" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129809204</v>
+        <v>129809831</v>
       </c>
       <c r="B18" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2415,34 +2415,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496151</v>
+        <v>496065</v>
       </c>
       <c r="R18" t="n">
-        <v>7040043</v>
+        <v>7040037</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,28 +2486,54 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129809831</v>
+        <v>129809204</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2512,37 +2541,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496065</v>
+        <v>496151</v>
       </c>
       <c r="R19" t="n">
-        <v>7040037</v>
+        <v>7040043</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,44 +2609,18 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2630,7 +2630,7 @@
         <v>129809213</v>
       </c>
       <c r="B20" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2855,34 +2855,30 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129809206</v>
+        <v>129809217</v>
       </c>
       <c r="B22" t="n">
-        <v>80215</v>
+        <v>91619</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2890,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496146</v>
+        <v>496090</v>
       </c>
       <c r="R22" t="n">
-        <v>7040041</v>
+        <v>7040205</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2952,30 +2948,34 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129809217</v>
+        <v>129809206</v>
       </c>
       <c r="B23" t="n">
-        <v>91617</v>
+        <v>80215</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496090</v>
+        <v>496146</v>
       </c>
       <c r="R23" t="n">
-        <v>7040205</v>
+        <v>7040041</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3048,7 +3048,7 @@
         <v>129809212</v>
       </c>
       <c r="B24" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 47128-2025 artfynd.xlsx
+++ b/artfynd/A 47128-2025 artfynd.xlsx
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129809833</v>
+        <v>129809205</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,37 +1025,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496073</v>
+        <v>496150</v>
       </c>
       <c r="R5" t="n">
-        <v>7040125</v>
+        <v>7040206</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,54 +1093,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129809205</v>
+        <v>129809833</v>
       </c>
       <c r="B6" t="n">
-        <v>91599</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,34 +1122,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496150</v>
+        <v>496073</v>
       </c>
       <c r="R6" t="n">
-        <v>7040206</v>
+        <v>7040125</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,18 +1193,44 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1851,32 +1851,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129809218</v>
+        <v>129809216</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>80146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496187</v>
+        <v>496144</v>
       </c>
       <c r="R13" t="n">
-        <v>7040066</v>
+        <v>7040037</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,32 +1948,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129809216</v>
+        <v>129809218</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496144</v>
+        <v>496187</v>
       </c>
       <c r="R14" t="n">
-        <v>7040037</v>
+        <v>7040066</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 47128-2025 artfynd.xlsx
+++ b/artfynd/A 47128-2025 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>129809838</v>
       </c>
       <c r="B4" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1111,37 +1111,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129809833</v>
+        <v>129809837</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>100979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1149,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496073</v>
+        <v>496143</v>
       </c>
       <c r="R6" t="n">
-        <v>7040125</v>
+        <v>7040098</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,27 +1204,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1237,42 +1222,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129809837</v>
+        <v>129809833</v>
       </c>
       <c r="B7" t="n">
-        <v>100969</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1280,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496143</v>
+        <v>496073</v>
       </c>
       <c r="R7" t="n">
-        <v>7040098</v>
+        <v>7040125</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1310,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1851,32 +1851,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129809216</v>
+        <v>129809218</v>
       </c>
       <c r="B13" t="n">
-        <v>80146</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496144</v>
+        <v>496187</v>
       </c>
       <c r="R13" t="n">
-        <v>7040037</v>
+        <v>7040066</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,32 +1948,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129809218</v>
+        <v>129809216</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496187</v>
+        <v>496144</v>
       </c>
       <c r="R14" t="n">
-        <v>7040066</v>
+        <v>7040037</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 47128-2025 artfynd.xlsx
+++ b/artfynd/A 47128-2025 artfynd.xlsx
@@ -1111,42 +1111,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129809837</v>
+        <v>129809833</v>
       </c>
       <c r="B6" t="n">
-        <v>100979</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1154,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496143</v>
+        <v>496073</v>
       </c>
       <c r="R6" t="n">
-        <v>7040098</v>
+        <v>7040125</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,7 +1199,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1222,37 +1237,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129809833</v>
+        <v>129809837</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>100979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1260,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496073</v>
+        <v>496143</v>
       </c>
       <c r="R7" t="n">
-        <v>7040125</v>
+        <v>7040098</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,27 +1330,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 47128-2025 artfynd.xlsx
+++ b/artfynd/A 47128-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129809835</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129809219</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129809838</v>
       </c>
       <c r="B4" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129809205</v>
       </c>
       <c r="B5" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>129809833</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>129809837</v>
       </c>
       <c r="B7" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>129809209</v>
       </c>
       <c r="B8" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>129809214</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>129809220</v>
       </c>
       <c r="B10" t="n">
-        <v>79337</v>
+        <v>79340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>129809208</v>
       </c>
       <c r="B11" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>129809215</v>
       </c>
       <c r="B12" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>129809218</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>129809216</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>129809830</v>
       </c>
       <c r="B15" t="n">
-        <v>80222</v>
+        <v>80225</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>129809834</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>129809211</v>
       </c>
       <c r="B17" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>129809831</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>129809204</v>
       </c>
       <c r="B19" t="n">
-        <v>83052</v>
+        <v>83055</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>129809213</v>
       </c>
       <c r="B20" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>129809832</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>129809217</v>
       </c>
       <c r="B22" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>129809206</v>
       </c>
       <c r="B23" t="n">
-        <v>80215</v>
+        <v>80218</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>129809212</v>
       </c>
       <c r="B24" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>129809207</v>
       </c>
       <c r="B25" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>129809829</v>
       </c>
       <c r="B26" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 47128-2025 artfynd.xlsx
+++ b/artfynd/A 47128-2025 artfynd.xlsx
@@ -675,37 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129809835</v>
+        <v>129809838</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>100983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496132</v>
+        <v>496154</v>
       </c>
       <c r="R2" t="n">
-        <v>7040056</v>
+        <v>7040081</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,24 +771,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129809219</v>
+        <v>129809835</v>
       </c>
       <c r="B3" t="n">
         <v>79084</v>
@@ -830,16 +820,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496160</v>
+        <v>496132</v>
       </c>
       <c r="R3" t="n">
-        <v>7040028</v>
+        <v>7040056</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,71 +873,89 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129809838</v>
+        <v>129809219</v>
       </c>
       <c r="B4" t="n">
-        <v>100983</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496154</v>
+        <v>496160</v>
       </c>
       <c r="R4" t="n">
-        <v>7040081</v>
+        <v>7040028</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,29 +996,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129809209</v>
+        <v>129809214</v>
       </c>
       <c r="B8" t="n">
-        <v>80189</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,34 +1359,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496144</v>
+        <v>496148</v>
       </c>
       <c r="R8" t="n">
-        <v>7040040</v>
+        <v>7040178</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,7 +1431,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Med apotechier</t>
+          <t>Färska ringhack högt upp på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129809214</v>
+        <v>129809209</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>80189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,42 +1469,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496148</v>
+        <v>496144</v>
       </c>
       <c r="R9" t="n">
-        <v>7040178</v>
+        <v>7040040</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack högt upp på gran</t>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 47128-2025 artfynd.xlsx
+++ b/artfynd/A 47128-2025 artfynd.xlsx
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129809214</v>
+        <v>129809209</v>
       </c>
       <c r="B8" t="n">
-        <v>57737</v>
+        <v>80189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,42 +1359,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496148</v>
+        <v>496144</v>
       </c>
       <c r="R8" t="n">
-        <v>7040178</v>
+        <v>7040040</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1423,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack högt upp på gran</t>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129809209</v>
+        <v>129809214</v>
       </c>
       <c r="B9" t="n">
-        <v>80189</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,34 +1461,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496144</v>
+        <v>496148</v>
       </c>
       <c r="R9" t="n">
-        <v>7040040</v>
+        <v>7040178</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Med apotechier</t>
+          <t>Färska ringhack högt upp på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 47128-2025 artfynd.xlsx
+++ b/artfynd/A 47128-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129809219</v>
+        <v>129809835</v>
       </c>
       <c r="B2" t="n">
         <v>79095</v>
@@ -704,16 +704,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496160</v>
+        <v>496132</v>
       </c>
       <c r="R2" t="n">
-        <v>7040028</v>
+        <v>7040056</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,71 +757,89 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129809838</v>
+        <v>129809219</v>
       </c>
       <c r="B3" t="n">
-        <v>101020</v>
+        <v>79095</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496154</v>
+        <v>496160</v>
       </c>
       <c r="R3" t="n">
-        <v>7040081</v>
+        <v>7040028</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,66 +880,60 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129809835</v>
+        <v>129809838</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>101020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -926,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496132</v>
+        <v>496154</v>
       </c>
       <c r="R4" t="n">
-        <v>7040056</v>
+        <v>7040081</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,24 +994,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129809833</v>
+        <v>129809205</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>91639</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,37 +1025,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496073</v>
+        <v>496150</v>
       </c>
       <c r="R5" t="n">
-        <v>7040125</v>
+        <v>7040206</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,54 +1093,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129809205</v>
+        <v>129809833</v>
       </c>
       <c r="B6" t="n">
-        <v>91639</v>
+        <v>79095</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,34 +1122,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496150</v>
+        <v>496073</v>
       </c>
       <c r="R6" t="n">
-        <v>7040206</v>
+        <v>7040125</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,18 +1193,44 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1851,32 +1851,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129809218</v>
+        <v>129809216</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>80160</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496187</v>
+        <v>496144</v>
       </c>
       <c r="R13" t="n">
-        <v>7040066</v>
+        <v>7040037</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,32 +1948,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129809216</v>
+        <v>129809218</v>
       </c>
       <c r="B14" t="n">
-        <v>80160</v>
+        <v>79095</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496144</v>
+        <v>496187</v>
       </c>
       <c r="R14" t="n">
-        <v>7040037</v>
+        <v>7040066</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 47128-2025 artfynd.xlsx
+++ b/artfynd/A 47128-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129809835</v>
+        <v>129809219</v>
       </c>
       <c r="B2" t="n">
         <v>79095</v>
@@ -704,19 +704,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496132</v>
+        <v>496160</v>
       </c>
       <c r="R2" t="n">
-        <v>7040056</v>
+        <v>7040028</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,89 +754,71 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129809219</v>
+        <v>129809838</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>101020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496160</v>
+        <v>496154</v>
       </c>
       <c r="R3" t="n">
-        <v>7040028</v>
+        <v>7040081</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,60 +859,66 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129809838</v>
+        <v>129809835</v>
       </c>
       <c r="B4" t="n">
-        <v>101020</v>
+        <v>79095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496154</v>
+        <v>496132</v>
       </c>
       <c r="R4" t="n">
-        <v>7040081</v>
+        <v>7040056</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,9 +979,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1851,32 +1851,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129809216</v>
+        <v>129809218</v>
       </c>
       <c r="B13" t="n">
-        <v>80160</v>
+        <v>79095</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496144</v>
+        <v>496187</v>
       </c>
       <c r="R13" t="n">
-        <v>7040037</v>
+        <v>7040066</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,32 +1948,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129809218</v>
+        <v>129809216</v>
       </c>
       <c r="B14" t="n">
-        <v>79095</v>
+        <v>80160</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496187</v>
+        <v>496144</v>
       </c>
       <c r="R14" t="n">
-        <v>7040066</v>
+        <v>7040037</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 47128-2025 artfynd.xlsx
+++ b/artfynd/A 47128-2025 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129809219</v>
+        <v>129809838</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>101022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496160</v>
+        <v>496154</v>
       </c>
       <c r="R2" t="n">
-        <v>7040028</v>
+        <v>7040081</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,60 +762,66 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129809838</v>
+        <v>129809835</v>
       </c>
       <c r="B3" t="n">
-        <v>101020</v>
+        <v>79095</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496154</v>
+        <v>496132</v>
       </c>
       <c r="R3" t="n">
-        <v>7040081</v>
+        <v>7040056</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,9 +882,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -888,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129809835</v>
+        <v>129809219</v>
       </c>
       <c r="B4" t="n">
         <v>79095</v>
@@ -917,19 +946,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496132</v>
+        <v>496160</v>
       </c>
       <c r="R4" t="n">
-        <v>7040056</v>
+        <v>7040028</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,44 +996,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
         <v>129809205</v>
       </c>
       <c r="B5" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,37 +1111,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129809833</v>
+        <v>129809837</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>101022</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1149,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496073</v>
+        <v>496143</v>
       </c>
       <c r="R6" t="n">
-        <v>7040125</v>
+        <v>7040098</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,27 +1204,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1237,42 +1222,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129809837</v>
+        <v>129809833</v>
       </c>
       <c r="B7" t="n">
-        <v>101020</v>
+        <v>79095</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1280,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496143</v>
+        <v>496073</v>
       </c>
       <c r="R7" t="n">
-        <v>7040098</v>
+        <v>7040125</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1310,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -2314,7 +2314,7 @@
         <v>129809211</v>
       </c>
       <c r="B17" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>129809213</v>
       </c>
       <c r="B20" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>129809217</v>
       </c>
       <c r="B22" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>129809212</v>
       </c>
       <c r="B24" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 47128-2025 artfynd.xlsx
+++ b/artfynd/A 47128-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129809838</v>
+        <v>129809205</v>
       </c>
       <c r="B2" t="n">
-        <v>101022</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496154</v>
+        <v>496150</v>
       </c>
       <c r="R2" t="n">
-        <v>7040081</v>
+        <v>7040206</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,39 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129809835</v>
+        <v>129809213</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,37 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496132</v>
+        <v>496090</v>
       </c>
       <c r="R3" t="n">
-        <v>7040056</v>
+        <v>7040212</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,76 +851,50 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129809219</v>
+        <v>129809212</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496160</v>
+        <v>496149</v>
       </c>
       <c r="R4" t="n">
-        <v>7040028</v>
+        <v>7040202</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129809205</v>
+        <v>129809218</v>
       </c>
       <c r="B5" t="n">
-        <v>91641</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496150</v>
+        <v>496187</v>
       </c>
       <c r="R5" t="n">
-        <v>7040206</v>
+        <v>7040066</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,53 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129809837</v>
+        <v>129809219</v>
       </c>
       <c r="B6" t="n">
-        <v>101022</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496143</v>
+        <v>496160</v>
       </c>
       <c r="R6" t="n">
-        <v>7040098</v>
+        <v>7040028</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,38 +1142,32 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129809833</v>
+        <v>129809831</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1260,10 +1198,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496073</v>
+        <v>496065</v>
       </c>
       <c r="R7" t="n">
-        <v>7040125</v>
+        <v>7040037</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1248,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1348,45 +1286,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129809209</v>
+        <v>129809832</v>
       </c>
       <c r="B8" t="n">
-        <v>80200</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496144</v>
+        <v>496081</v>
       </c>
       <c r="R8" t="n">
-        <v>7040040</v>
+        <v>7040055</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,7 +1364,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Med apotechier</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,60 +1373,81 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129809214</v>
+        <v>129809833</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1493,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496148</v>
+        <v>496073</v>
       </c>
       <c r="R9" t="n">
-        <v>7040178</v>
+        <v>7040125</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,74 +1493,98 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack högt upp på gran</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129809220</v>
+        <v>129809834</v>
       </c>
       <c r="B10" t="n">
-        <v>79351</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496038</v>
+        <v>496148</v>
       </c>
       <c r="R10" t="n">
-        <v>7040065</v>
+        <v>7040050</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,69 +1619,103 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gran i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129809208</v>
+        <v>129809835</v>
       </c>
       <c r="B11" t="n">
-        <v>80200</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496064</v>
+        <v>496132</v>
       </c>
       <c r="R11" t="n">
-        <v>7040152</v>
+        <v>7040056</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,28 +1756,54 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129809215</v>
+        <v>129809204</v>
       </c>
       <c r="B12" t="n">
-        <v>57900</v>
+        <v>83307</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1789,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496145</v>
+        <v>496151</v>
       </c>
       <c r="R12" t="n">
-        <v>7040051</v>
+        <v>7040043</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,10 +1897,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129809218</v>
+        <v>129809207</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1862,21 +1908,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496187</v>
+        <v>496017</v>
       </c>
       <c r="R13" t="n">
-        <v>7040066</v>
+        <v>7040054</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,32 +1994,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129809216</v>
+        <v>129809208</v>
       </c>
       <c r="B14" t="n">
-        <v>80160</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1983,10 +2029,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496144</v>
+        <v>496064</v>
       </c>
       <c r="R14" t="n">
-        <v>7040037</v>
+        <v>7040152</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,52 +2091,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129809830</v>
+        <v>129809209</v>
       </c>
       <c r="B15" t="n">
-        <v>80236</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496111</v>
+        <v>496144</v>
       </c>
       <c r="R15" t="n">
-        <v>7040057</v>
+        <v>7040040</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,7 +2166,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På en levande lutande sälg.</t>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2136,54 +2175,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129809834</v>
+        <v>129809829</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2191,26 +2204,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2218,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496148</v>
+        <v>496118</v>
       </c>
       <c r="R16" t="n">
-        <v>7040050</v>
+        <v>7040052</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,7 +2275,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Växer på en levande lutande sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,22 +2295,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2311,30 +2328,34 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129809211</v>
+        <v>129809220</v>
       </c>
       <c r="B17" t="n">
-        <v>91661</v>
+        <v>79583</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6459</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2342,10 +2363,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496062</v>
+        <v>496038</v>
       </c>
       <c r="R17" t="n">
-        <v>7040149</v>
+        <v>7040065</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2404,48 +2425,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129809831</v>
+        <v>129809206</v>
       </c>
       <c r="B18" t="n">
-        <v>79095</v>
+        <v>80461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496065</v>
+        <v>496146</v>
       </c>
       <c r="R18" t="n">
-        <v>7040037</v>
+        <v>7040041</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,89 +2504,70 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129809204</v>
+        <v>129809830</v>
       </c>
       <c r="B19" t="n">
-        <v>83073</v>
+        <v>80468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496151</v>
+        <v>496111</v>
       </c>
       <c r="R19" t="n">
-        <v>7040043</v>
+        <v>7040057</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2603,34 +2602,65 @@
           <t>2025-11-23</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På en levande lutande sälg.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129809213</v>
+        <v>129809214</v>
       </c>
       <c r="B20" t="n">
-        <v>91641</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2638,34 +2668,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496090</v>
+        <v>496148</v>
       </c>
       <c r="R20" t="n">
-        <v>7040212</v>
+        <v>7040178</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,6 +2736,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack högt upp på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2724,10 +2767,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129809832</v>
+        <v>129809215</v>
       </c>
       <c r="B21" t="n">
-        <v>79095</v>
+        <v>58114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2735,37 +2778,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496081</v>
+        <v>496145</v>
       </c>
       <c r="R21" t="n">
-        <v>7040055</v>
+        <v>7040051</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,96 +2840,77 @@
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På gran i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129809217</v>
+        <v>129809837</v>
       </c>
       <c r="B22" t="n">
-        <v>91661</v>
+        <v>101325</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496090</v>
+        <v>496143</v>
       </c>
       <c r="R22" t="n">
-        <v>7040205</v>
+        <v>7040098</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2930,28 +2951,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129809206</v>
+        <v>129809838</v>
       </c>
       <c r="B23" t="n">
-        <v>80229</v>
+        <v>101325</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2959,34 +2986,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gulåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496146</v>
+        <v>496154</v>
       </c>
       <c r="R23" t="n">
-        <v>7040041</v>
+        <v>7040081</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3027,28 +3062,39 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129809212</v>
+        <v>129809216</v>
       </c>
       <c r="B24" t="n">
-        <v>91605</v>
+        <v>80392</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3056,21 +3102,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3080,10 +3126,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496149</v>
+        <v>496144</v>
       </c>
       <c r="R24" t="n">
-        <v>7040202</v>
+        <v>7040037</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3139,238 +3185,6 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>129809207</v>
-      </c>
-      <c r="B25" t="n">
-        <v>80200</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Gulåstjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>496017</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7040054</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Häggenås</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Marielle Löthman</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Marielle Löthman</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>129809829</v>
-      </c>
-      <c r="B26" t="n">
-        <v>80200</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Gulåstjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>496118</v>
-      </c>
-      <c r="R26" t="n">
-        <v>7040052</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Häggenås</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Växer på en levande lutande sälg.</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47128-2025 artfynd.xlsx
+++ b/artfynd/A 47128-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809205</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809213</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809212</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809218</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809219</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809831</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809832</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1540,6 +1580,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809833</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809834</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1797,6 +1847,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809835</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1894,6 +1949,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809204</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1991,6 +2051,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809207</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2088,6 +2153,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809208</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2190,6 +2260,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809209</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2325,6 +2400,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809829</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2422,6 +2502,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809220</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2519,6 +2604,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809206</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2654,6 +2744,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809830</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2764,6 +2859,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809214</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2861,6 +2961,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809215</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2972,6 +3077,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809837</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3088,6 +3198,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809838</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3185,8 +3300,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809216</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>